--- a/PsychoPy-local/fpjt_files/Messages.xlsx
+++ b/PsychoPy-local/fpjt_files/Messages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cdabb12e9f34f4c5/10_Paper/105_MIA/10_BAS_Collab/FPJT/PsychoPy-local/fpjt_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cdabb12e9f34f4c5/10_Paper/105_MIA/03_Platform/FPJT/PsychoPy-local/fpjt_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="295" documentId="8_{9A5DEF40-44A6-4D82-8A38-CC73A1DAE49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCDF1712-72CB-45BD-87D6-102251390C5C}"/>
+  <xr:revisionPtr revIDLastSave="297" documentId="8_{9A5DEF40-44A6-4D82-8A38-CC73A1DAE49D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00332C86-7681-4FF1-B20B-DD4A1E5FD7F9}"/>
   <bookViews>
-    <workbookView xWindow="44880" yWindow="11850" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -971,9 +971,6 @@
     <t>Droite</t>
   </si>
   <si>
-    <t>Rechte</t>
-  </si>
-  <si>
     <t>You will now hear an audio instruction in 36 trials, each containing 3 to 7 consecutive movements. IMAGINE what it LOOKS LIKE and how it FEELS to perform these movements YOURSELF. Remain seated calmly, CLOSE YOUR EYES and DO NOT MOVE.
 The length of the audio instruction varies randomly. Each audio instruction BEGINS with imagining an upright, standing position. Change your body position IN YOUR IMAGERY according to the instructed movements.
 OPEN your eyes at the SIGNAL TONE. An image of a person seen from behind will appear. Decide as QUICKLY AND ACCURATELY as possible whether the position of this person matches your final position in your imagery.
@@ -1195,6 +1192,9 @@
     <t>Rappel :
 Imaginez À QUOI CELA RESSEMBLE et CE QUE L’ON RESSENT en exécutant vous-même les mouvements décrits dans l’instruction audio.
 Ouvrez les yeux lorsque vous entendez le signal sonore. Décidez aussi RAPIDEMENT ET CORRECTEMENT que possible si l’image affichée correspond à la position finale dans votre imagerie.</t>
+  </si>
+  <si>
+    <t>Rechts</t>
   </si>
 </sst>
 </file>
@@ -1669,16 +1669,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>322</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
@@ -2111,16 +2111,16 @@
         <v>142</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="199.5" x14ac:dyDescent="0.45">
@@ -2128,16 +2128,16 @@
         <v>143</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="199.5" x14ac:dyDescent="0.45">
@@ -2145,16 +2145,16 @@
         <v>144</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
@@ -2162,16 +2162,16 @@
         <v>145</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
@@ -2179,16 +2179,16 @@
         <v>146</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
@@ -2417,16 +2417,16 @@
         <v>192</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
@@ -2434,16 +2434,16 @@
         <v>193</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
@@ -2451,16 +2451,16 @@
         <v>194</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
@@ -2468,16 +2468,16 @@
         <v>196</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>205</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
@@ -2502,16 +2502,16 @@
         <v>199</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="14.25" x14ac:dyDescent="0.45">
@@ -2794,7 +2794,7 @@
         <v>307</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>310</v>
+        <v>353</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>308</v>
@@ -2832,21 +2832,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9F5CAB0486A994CA2C3B13E059EF2AE" ma:contentTypeVersion="0" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8645ec4a60d0c8c7009d2d6675847a91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636d7205651659ec4fcda0bcbde9384b">
     <xsd:element name="properties">
@@ -2960,7 +2945,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -2975,26 +2991,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>